--- a/assets/infobasica/planilhas/aula22_nivel2.xlsx
+++ b/assets/infobasica/planilhas/aula22_nivel2.xlsx
@@ -1034,7 +1034,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Resfriamento: 200 em B2 e =B2-0,1(B2-25) em B3, arrastado; =CONT.SE(B2:B60; "&gt;=40") conta os minutos acima de 40 °C.</t>
+          <t>Resfriamento: 200 em B2 e =B2-0,1*(B2-25) em B3, arrastado; =CONT.SE(B2:B60; "&gt;=40") conta os minutos acima de 40 °C.</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
